--- a/out/AI-Capability-Model.xlsx
+++ b/out/AI-Capability-Model.xlsx
@@ -708,7 +708,7 @@
     <row r="2">
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Facts, one scale, generated views  ·  IDB Enterprise Architecture</t>
+          <t>A capability model for AI  ·  Inter-American Development Bank</t>
         </is>
       </c>
     </row>
@@ -786,7 +786,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="14" customHeight="1">
+    <row r="12" ht="24.8" customHeight="1">
       <c r="B12" s="4" t="inlineStr">
         <is>
           <t>Defined</t>
@@ -794,7 +794,7 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>Is there a published Bank standard or method for this?</t>
+          <t>Is there an approved institutional standard, policy or method? Whoever owns the subject sets it - the platform team, Cybersecurity, Data Management, Legal, HR or EA. Not one function's job.</t>
         </is>
       </c>
     </row>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="D5" s="13" t="inlineStr">
         <is>
-          <t>Is there a published Bank standard or method for this?</t>
+          <t>Is there an approved institutional standard, policy or method for this? Set by whoever owns the subject - the platform team, Cybersecurity, Data Management, Legal, HR or EA.</t>
         </is>
       </c>
       <c r="E5" s="25" t="inlineStr">
@@ -4893,7 +4893,7 @@
       <c r="H5" s="27" t="inlineStr"/>
       <c r="I5" s="13" t="inlineStr">
         <is>
-          <t>No Bank standard found in the asset register - confirm none exists</t>
+          <t>No approved standard found in the asset register. The asset register currently covers AI platform assets only, so a standard owned by another function may exist and not be recorded here - confirm with the owner.</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="D9" s="13" t="inlineStr">
         <is>
-          <t>Is there a published Bank standard or method for this?</t>
+          <t>Is there an approved institutional standard, policy or method for this? Set by whoever owns the subject - the platform team, Cybersecurity, Data Management, Legal, HR or EA.</t>
         </is>
       </c>
       <c r="E9" s="25" t="inlineStr">
@@ -5041,7 +5041,7 @@
       <c r="H9" s="27" t="inlineStr"/>
       <c r="I9" s="13" t="inlineStr">
         <is>
-          <t>No Bank standard found in the asset register - confirm none exists</t>
+          <t>No approved standard found in the asset register. The asset register currently covers AI platform assets only, so a standard owned by another function may exist and not be recorded here - confirm with the owner.</t>
         </is>
       </c>
     </row>
@@ -5176,7 +5176,7 @@
       </c>
       <c r="D13" s="13" t="inlineStr">
         <is>
-          <t>Is there a published Bank standard or method for this?</t>
+          <t>Is there an approved institutional standard, policy or method for this? Set by whoever owns the subject - the platform team, Cybersecurity, Data Management, Legal, HR or EA.</t>
         </is>
       </c>
       <c r="E13" s="25" t="inlineStr">
@@ -5189,7 +5189,7 @@
       <c r="H13" s="27" t="inlineStr"/>
       <c r="I13" s="13" t="inlineStr">
         <is>
-          <t>No Bank standard found in the asset register - confirm none exists</t>
+          <t>No approved standard found in the asset register. The asset register currently covers AI platform assets only, so a standard owned by another function may exist and not be recorded here - confirm with the owner.</t>
         </is>
       </c>
     </row>
@@ -5324,7 +5324,7 @@
       </c>
       <c r="D17" s="13" t="inlineStr">
         <is>
-          <t>Is there a published Bank standard or method for this?</t>
+          <t>Is there an approved institutional standard, policy or method for this? Set by whoever owns the subject - the platform team, Cybersecurity, Data Management, Legal, HR or EA.</t>
         </is>
       </c>
       <c r="E17" s="25" t="inlineStr">
@@ -5337,7 +5337,7 @@
       <c r="H17" s="27" t="inlineStr"/>
       <c r="I17" s="13" t="inlineStr">
         <is>
-          <t>No Bank standard found in the asset register - confirm none exists</t>
+          <t>No approved standard found in the asset register. The asset register currently covers AI platform assets only, so a standard owned by another function may exist and not be recorded here - confirm with the owner.</t>
         </is>
       </c>
     </row>
@@ -5472,7 +5472,7 @@
       </c>
       <c r="D21" s="13" t="inlineStr">
         <is>
-          <t>Is there a published Bank standard or method for this?</t>
+          <t>Is there an approved institutional standard, policy or method for this? Set by whoever owns the subject - the platform team, Cybersecurity, Data Management, Legal, HR or EA.</t>
         </is>
       </c>
       <c r="E21" s="25" t="inlineStr">
@@ -5485,7 +5485,7 @@
       <c r="H21" s="27" t="inlineStr"/>
       <c r="I21" s="13" t="inlineStr">
         <is>
-          <t>No Bank standard found in the asset register - confirm none exists</t>
+          <t>No approved standard found in the asset register. The asset register currently covers AI platform assets only, so a standard owned by another function may exist and not be recorded here - confirm with the owner.</t>
         </is>
       </c>
     </row>
@@ -5620,7 +5620,7 @@
       </c>
       <c r="D25" s="13" t="inlineStr">
         <is>
-          <t>Is there a published Bank standard or method for this?</t>
+          <t>Is there an approved institutional standard, policy or method for this? Set by whoever owns the subject - the platform team, Cybersecurity, Data Management, Legal, HR or EA.</t>
         </is>
       </c>
       <c r="E25" s="25" t="inlineStr">
@@ -5633,7 +5633,7 @@
       <c r="H25" s="27" t="inlineStr"/>
       <c r="I25" s="13" t="inlineStr">
         <is>
-          <t>No Bank standard found in the asset register - confirm none exists</t>
+          <t>No approved standard found in the asset register. The asset register currently covers AI platform assets only, so a standard owned by another function may exist and not be recorded here - confirm with the owner.</t>
         </is>
       </c>
     </row>
@@ -5772,7 +5772,7 @@
       </c>
       <c r="D29" s="13" t="inlineStr">
         <is>
-          <t>Is there a published Bank standard or method for this?</t>
+          <t>Is there an approved institutional standard, policy or method for this? Set by whoever owns the subject - the platform team, Cybersecurity, Data Management, Legal, HR or EA.</t>
         </is>
       </c>
       <c r="E29" s="30" t="inlineStr">
@@ -5797,7 +5797,7 @@
       </c>
       <c r="I29" s="13" t="inlineStr">
         <is>
-          <t>Published standard and reference architecture</t>
+          <t>Approved standard and reference architecture published</t>
         </is>
       </c>
     </row>
@@ -5932,7 +5932,7 @@
       </c>
       <c r="D33" s="13" t="inlineStr">
         <is>
-          <t>Is there a published Bank standard or method for this?</t>
+          <t>Is there an approved institutional standard, policy or method for this? Set by whoever owns the subject - the platform team, Cybersecurity, Data Management, Legal, HR or EA.</t>
         </is>
       </c>
       <c r="E33" s="25" t="inlineStr">
@@ -5945,7 +5945,7 @@
       <c r="H33" s="27" t="inlineStr"/>
       <c r="I33" s="13" t="inlineStr">
         <is>
-          <t>No Bank standard found in the asset register - confirm none exists</t>
+          <t>No approved standard found in the asset register. The asset register currently covers AI platform assets only, so a standard owned by another function may exist and not be recorded here - confirm with the owner.</t>
         </is>
       </c>
     </row>
@@ -6080,7 +6080,7 @@
       </c>
       <c r="D37" s="13" t="inlineStr">
         <is>
-          <t>Is there a published Bank standard or method for this?</t>
+          <t>Is there an approved institutional standard, policy or method for this? Set by whoever owns the subject - the platform team, Cybersecurity, Data Management, Legal, HR or EA.</t>
         </is>
       </c>
       <c r="E37" s="25" t="inlineStr">
@@ -6093,7 +6093,7 @@
       <c r="H37" s="27" t="inlineStr"/>
       <c r="I37" s="13" t="inlineStr">
         <is>
-          <t>No Bank standard found in the asset register - confirm none exists</t>
+          <t>No approved standard found in the asset register. The asset register currently covers AI platform assets only, so a standard owned by another function may exist and not be recorded here - confirm with the owner.</t>
         </is>
       </c>
     </row>
@@ -6232,7 +6232,7 @@
       </c>
       <c r="D41" s="13" t="inlineStr">
         <is>
-          <t>Is there a published Bank standard or method for this?</t>
+          <t>Is there an approved institutional standard, policy or method for this? Set by whoever owns the subject - the platform team, Cybersecurity, Data Management, Legal, HR or EA.</t>
         </is>
       </c>
       <c r="E41" s="30" t="inlineStr">
@@ -6257,7 +6257,7 @@
       </c>
       <c r="I41" s="13" t="inlineStr">
         <is>
-          <t>Published standard and reference architecture</t>
+          <t>Approved standard and reference architecture published</t>
         </is>
       </c>
     </row>
@@ -6392,7 +6392,7 @@
       </c>
       <c r="D45" s="13" t="inlineStr">
         <is>
-          <t>Is there a published Bank standard or method for this?</t>
+          <t>Is there an approved institutional standard, policy or method for this? Set by whoever owns the subject - the platform team, Cybersecurity, Data Management, Legal, HR or EA.</t>
         </is>
       </c>
       <c r="E45" s="25" t="inlineStr">
@@ -6405,7 +6405,7 @@
       <c r="H45" s="27" t="inlineStr"/>
       <c r="I45" s="13" t="inlineStr">
         <is>
-          <t>No Bank standard found in the asset register - confirm none exists</t>
+          <t>No approved standard found in the asset register. The asset register currently covers AI platform assets only, so a standard owned by another function may exist and not be recorded here - confirm with the owner.</t>
         </is>
       </c>
     </row>
@@ -6540,7 +6540,7 @@
       </c>
       <c r="D49" s="13" t="inlineStr">
         <is>
-          <t>Is there a published Bank standard or method for this?</t>
+          <t>Is there an approved institutional standard, policy or method for this? Set by whoever owns the subject - the platform team, Cybersecurity, Data Management, Legal, HR or EA.</t>
         </is>
       </c>
       <c r="E49" s="25" t="inlineStr">
@@ -6553,7 +6553,7 @@
       <c r="H49" s="27" t="inlineStr"/>
       <c r="I49" s="13" t="inlineStr">
         <is>
-          <t>No Bank standard found in the asset register - confirm none exists</t>
+          <t>No approved standard found in the asset register. The asset register currently covers AI platform assets only, so a standard owned by another function may exist and not be recorded here - confirm with the owner.</t>
         </is>
       </c>
     </row>
@@ -6688,7 +6688,7 @@
       </c>
       <c r="D53" s="13" t="inlineStr">
         <is>
-          <t>Is there a published Bank standard or method for this?</t>
+          <t>Is there an approved institutional standard, policy or method for this? Set by whoever owns the subject - the platform team, Cybersecurity, Data Management, Legal, HR or EA.</t>
         </is>
       </c>
       <c r="E53" s="25" t="inlineStr">
@@ -6701,7 +6701,7 @@
       <c r="H53" s="27" t="inlineStr"/>
       <c r="I53" s="13" t="inlineStr">
         <is>
-          <t>No Bank standard found in the asset register - confirm none exists</t>
+          <t>No approved standard found in the asset register. The asset register currently covers AI platform assets only, so a standard owned by another function may exist and not be recorded here - confirm with the owner.</t>
         </is>
       </c>
     </row>
@@ -6836,7 +6836,7 @@
       </c>
       <c r="D57" s="13" t="inlineStr">
         <is>
-          <t>Is there a published Bank standard or method for this?</t>
+          <t>Is there an approved institutional standard, policy or method for this? Set by whoever owns the subject - the platform team, Cybersecurity, Data Management, Legal, HR or EA.</t>
         </is>
       </c>
       <c r="E57" s="25" t="inlineStr">
@@ -6849,7 +6849,7 @@
       <c r="H57" s="27" t="inlineStr"/>
       <c r="I57" s="13" t="inlineStr">
         <is>
-          <t>No Bank standard found in the asset register - confirm none exists</t>
+          <t>No approved standard found in the asset register. The asset register currently covers AI platform assets only, so a standard owned by another function may exist and not be recorded here - confirm with the owner.</t>
         </is>
       </c>
     </row>
@@ -6984,7 +6984,7 @@
       </c>
       <c r="D61" s="13" t="inlineStr">
         <is>
-          <t>Is there a published Bank standard or method for this?</t>
+          <t>Is there an approved institutional standard, policy or method for this? Set by whoever owns the subject - the platform team, Cybersecurity, Data Management, Legal, HR or EA.</t>
         </is>
       </c>
       <c r="E61" s="25" t="inlineStr">
@@ -6997,7 +6997,7 @@
       <c r="H61" s="27" t="inlineStr"/>
       <c r="I61" s="13" t="inlineStr">
         <is>
-          <t>No Bank standard found in the asset register - confirm none exists</t>
+          <t>No approved standard found in the asset register. The asset register currently covers AI platform assets only, so a standard owned by another function may exist and not be recorded here - confirm with the owner.</t>
         </is>
       </c>
     </row>
@@ -7136,7 +7136,7 @@
       </c>
       <c r="D65" s="13" t="inlineStr">
         <is>
-          <t>Is there a published Bank standard or method for this?</t>
+          <t>Is there an approved institutional standard, policy or method for this? Set by whoever owns the subject - the platform team, Cybersecurity, Data Management, Legal, HR or EA.</t>
         </is>
       </c>
       <c r="E65" s="30" t="inlineStr">
@@ -7161,7 +7161,7 @@
       </c>
       <c r="I65" s="13" t="inlineStr">
         <is>
-          <t>Published standard and reference architecture</t>
+          <t>Approved standard and reference architecture published</t>
         </is>
       </c>
     </row>
@@ -7300,7 +7300,7 @@
       </c>
       <c r="D69" s="13" t="inlineStr">
         <is>
-          <t>Is there a published Bank standard or method for this?</t>
+          <t>Is there an approved institutional standard, policy or method for this? Set by whoever owns the subject - the platform team, Cybersecurity, Data Management, Legal, HR or EA.</t>
         </is>
       </c>
       <c r="E69" s="30" t="inlineStr">
@@ -7325,7 +7325,7 @@
       </c>
       <c r="I69" s="13" t="inlineStr">
         <is>
-          <t>Published standard and reference architecture</t>
+          <t>Approved standard and reference architecture published</t>
         </is>
       </c>
     </row>
@@ -7460,7 +7460,7 @@
       </c>
       <c r="D73" s="13" t="inlineStr">
         <is>
-          <t>Is there a published Bank standard or method for this?</t>
+          <t>Is there an approved institutional standard, policy or method for this? Set by whoever owns the subject - the platform team, Cybersecurity, Data Management, Legal, HR or EA.</t>
         </is>
       </c>
       <c r="E73" s="25" t="inlineStr">
@@ -7473,7 +7473,7 @@
       <c r="H73" s="27" t="inlineStr"/>
       <c r="I73" s="13" t="inlineStr">
         <is>
-          <t>No Bank standard found in the asset register - confirm none exists</t>
+          <t>No approved standard found in the asset register. The asset register currently covers AI platform assets only, so a standard owned by another function may exist and not be recorded here - confirm with the owner.</t>
         </is>
       </c>
     </row>
@@ -7612,7 +7612,7 @@
       </c>
       <c r="D77" s="13" t="inlineStr">
         <is>
-          <t>Is there a published Bank standard or method for this?</t>
+          <t>Is there an approved institutional standard, policy or method for this? Set by whoever owns the subject - the platform team, Cybersecurity, Data Management, Legal, HR or EA.</t>
         </is>
       </c>
       <c r="E77" s="30" t="inlineStr">
@@ -7637,7 +7637,7 @@
       </c>
       <c r="I77" s="13" t="inlineStr">
         <is>
-          <t>Published standard and reference architecture</t>
+          <t>Approved standard and reference architecture published</t>
         </is>
       </c>
     </row>
@@ -7772,7 +7772,7 @@
       </c>
       <c r="D81" s="13" t="inlineStr">
         <is>
-          <t>Is there a published Bank standard or method for this?</t>
+          <t>Is there an approved institutional standard, policy or method for this? Set by whoever owns the subject - the platform team, Cybersecurity, Data Management, Legal, HR or EA.</t>
         </is>
       </c>
       <c r="E81" s="25" t="inlineStr">
@@ -7785,7 +7785,7 @@
       <c r="H81" s="27" t="inlineStr"/>
       <c r="I81" s="13" t="inlineStr">
         <is>
-          <t>No Bank standard found in the asset register - confirm none exists</t>
+          <t>No approved standard found in the asset register. The asset register currently covers AI platform assets only, so a standard owned by another function may exist and not be recorded here - confirm with the owner.</t>
         </is>
       </c>
     </row>
@@ -7920,7 +7920,7 @@
       </c>
       <c r="D85" s="13" t="inlineStr">
         <is>
-          <t>Is there a published Bank standard or method for this?</t>
+          <t>Is there an approved institutional standard, policy or method for this? Set by whoever owns the subject - the platform team, Cybersecurity, Data Management, Legal, HR or EA.</t>
         </is>
       </c>
       <c r="E85" s="25" t="inlineStr">
@@ -7933,7 +7933,7 @@
       <c r="H85" s="27" t="inlineStr"/>
       <c r="I85" s="13" t="inlineStr">
         <is>
-          <t>No Bank standard found in the asset register - confirm none exists</t>
+          <t>No approved standard found in the asset register. The asset register currently covers AI platform assets only, so a standard owned by another function may exist and not be recorded here - confirm with the owner.</t>
         </is>
       </c>
     </row>
@@ -8072,7 +8072,7 @@
       </c>
       <c r="D89" s="13" t="inlineStr">
         <is>
-          <t>Is there a published Bank standard or method for this?</t>
+          <t>Is there an approved institutional standard, policy or method for this? Set by whoever owns the subject - the platform team, Cybersecurity, Data Management, Legal, HR or EA.</t>
         </is>
       </c>
       <c r="E89" s="31" t="inlineStr">
@@ -8236,7 +8236,7 @@
       </c>
       <c r="D93" s="13" t="inlineStr">
         <is>
-          <t>Is there a published Bank standard or method for this?</t>
+          <t>Is there an approved institutional standard, policy or method for this? Set by whoever owns the subject - the platform team, Cybersecurity, Data Management, Legal, HR or EA.</t>
         </is>
       </c>
       <c r="E93" s="30" t="inlineStr">
@@ -8261,7 +8261,7 @@
       </c>
       <c r="I93" s="13" t="inlineStr">
         <is>
-          <t>Published standard and reference architecture</t>
+          <t>Approved standard and reference architecture published</t>
         </is>
       </c>
     </row>
@@ -8396,7 +8396,7 @@
       </c>
       <c r="D97" s="13" t="inlineStr">
         <is>
-          <t>Is there a published Bank standard or method for this?</t>
+          <t>Is there an approved institutional standard, policy or method for this? Set by whoever owns the subject - the platform team, Cybersecurity, Data Management, Legal, HR or EA.</t>
         </is>
       </c>
       <c r="E97" s="25" t="inlineStr">
@@ -8409,7 +8409,7 @@
       <c r="H97" s="27" t="inlineStr"/>
       <c r="I97" s="13" t="inlineStr">
         <is>
-          <t>No Bank standard found in the asset register - confirm none exists</t>
+          <t>No approved standard found in the asset register. The asset register currently covers AI platform assets only, so a standard owned by another function may exist and not be recorded here - confirm with the owner.</t>
         </is>
       </c>
     </row>
@@ -8544,7 +8544,7 @@
       </c>
       <c r="D101" s="13" t="inlineStr">
         <is>
-          <t>Is there a published Bank standard or method for this?</t>
+          <t>Is there an approved institutional standard, policy or method for this? Set by whoever owns the subject - the platform team, Cybersecurity, Data Management, Legal, HR or EA.</t>
         </is>
       </c>
       <c r="E101" s="25" t="inlineStr">
@@ -8557,7 +8557,7 @@
       <c r="H101" s="27" t="inlineStr"/>
       <c r="I101" s="13" t="inlineStr">
         <is>
-          <t>No Bank standard found in the asset register - confirm none exists</t>
+          <t>No approved standard found in the asset register. The asset register currently covers AI platform assets only, so a standard owned by another function may exist and not be recorded here - confirm with the owner.</t>
         </is>
       </c>
     </row>
@@ -8696,7 +8696,7 @@
       </c>
       <c r="D105" s="13" t="inlineStr">
         <is>
-          <t>Is there a published Bank standard or method for this?</t>
+          <t>Is there an approved institutional standard, policy or method for this? Set by whoever owns the subject - the platform team, Cybersecurity, Data Management, Legal, HR or EA.</t>
         </is>
       </c>
       <c r="E105" s="31" t="inlineStr">
@@ -8860,7 +8860,7 @@
       </c>
       <c r="D109" s="13" t="inlineStr">
         <is>
-          <t>Is there a published Bank standard or method for this?</t>
+          <t>Is there an approved institutional standard, policy or method for this? Set by whoever owns the subject - the platform team, Cybersecurity, Data Management, Legal, HR or EA.</t>
         </is>
       </c>
       <c r="E109" s="30" t="inlineStr">
@@ -8885,7 +8885,7 @@
       </c>
       <c r="I109" s="13" t="inlineStr">
         <is>
-          <t>Published standard and reference architecture</t>
+          <t>Approved standard and reference architecture published</t>
         </is>
       </c>
     </row>
@@ -9024,7 +9024,7 @@
       </c>
       <c r="D113" s="13" t="inlineStr">
         <is>
-          <t>Is there a published Bank standard or method for this?</t>
+          <t>Is there an approved institutional standard, policy or method for this? Set by whoever owns the subject - the platform team, Cybersecurity, Data Management, Legal, HR or EA.</t>
         </is>
       </c>
       <c r="E113" s="30" t="inlineStr">
@@ -9049,7 +9049,7 @@
       </c>
       <c r="I113" s="13" t="inlineStr">
         <is>
-          <t>Published standard and reference architecture</t>
+          <t>Approved standard and reference architecture published</t>
         </is>
       </c>
     </row>
@@ -9188,7 +9188,7 @@
       </c>
       <c r="D117" s="13" t="inlineStr">
         <is>
-          <t>Is there a published Bank standard or method for this?</t>
+          <t>Is there an approved institutional standard, policy or method for this? Set by whoever owns the subject - the platform team, Cybersecurity, Data Management, Legal, HR or EA.</t>
         </is>
       </c>
       <c r="E117" s="30" t="inlineStr">
@@ -9213,7 +9213,7 @@
       </c>
       <c r="I117" s="13" t="inlineStr">
         <is>
-          <t>Published standard and reference architecture</t>
+          <t>Approved standard and reference architecture published</t>
         </is>
       </c>
     </row>
@@ -9352,7 +9352,7 @@
       </c>
       <c r="D121" s="13" t="inlineStr">
         <is>
-          <t>Is there a published Bank standard or method for this?</t>
+          <t>Is there an approved institutional standard, policy or method for this? Set by whoever owns the subject - the platform team, Cybersecurity, Data Management, Legal, HR or EA.</t>
         </is>
       </c>
       <c r="E121" s="30" t="inlineStr">
@@ -9377,7 +9377,7 @@
       </c>
       <c r="I121" s="13" t="inlineStr">
         <is>
-          <t>Published standard and reference architecture</t>
+          <t>Approved standard and reference architecture published</t>
         </is>
       </c>
     </row>
@@ -9516,7 +9516,7 @@
       </c>
       <c r="D125" s="13" t="inlineStr">
         <is>
-          <t>Is there a published Bank standard or method for this?</t>
+          <t>Is there an approved institutional standard, policy or method for this? Set by whoever owns the subject - the platform team, Cybersecurity, Data Management, Legal, HR or EA.</t>
         </is>
       </c>
       <c r="E125" s="31" t="inlineStr">
@@ -9676,7 +9676,7 @@
       </c>
       <c r="D129" s="13" t="inlineStr">
         <is>
-          <t>Is there a published Bank standard or method for this?</t>
+          <t>Is there an approved institutional standard, policy or method for this? Set by whoever owns the subject - the platform team, Cybersecurity, Data Management, Legal, HR or EA.</t>
         </is>
       </c>
       <c r="E129" s="25" t="inlineStr">
@@ -9689,7 +9689,7 @@
       <c r="H129" s="27" t="inlineStr"/>
       <c r="I129" s="13" t="inlineStr">
         <is>
-          <t>No Bank standard found in the asset register - confirm none exists</t>
+          <t>No approved standard found in the asset register. The asset register currently covers AI platform assets only, so a standard owned by another function may exist and not be recorded here - confirm with the owner.</t>
         </is>
       </c>
     </row>
@@ -9824,7 +9824,7 @@
       </c>
       <c r="D133" s="13" t="inlineStr">
         <is>
-          <t>Is there a published Bank standard or method for this?</t>
+          <t>Is there an approved institutional standard, policy or method for this? Set by whoever owns the subject - the platform team, Cybersecurity, Data Management, Legal, HR or EA.</t>
         </is>
       </c>
       <c r="E133" s="25" t="inlineStr">
@@ -9837,7 +9837,7 @@
       <c r="H133" s="27" t="inlineStr"/>
       <c r="I133" s="13" t="inlineStr">
         <is>
-          <t>No Bank standard found in the asset register - confirm none exists</t>
+          <t>No approved standard found in the asset register. The asset register currently covers AI platform assets only, so a standard owned by another function may exist and not be recorded here - confirm with the owner.</t>
         </is>
       </c>
     </row>
@@ -9972,7 +9972,7 @@
       </c>
       <c r="D137" s="13" t="inlineStr">
         <is>
-          <t>Is there a published Bank standard or method for this?</t>
+          <t>Is there an approved institutional standard, policy or method for this? Set by whoever owns the subject - the platform team, Cybersecurity, Data Management, Legal, HR or EA.</t>
         </is>
       </c>
       <c r="E137" s="25" t="inlineStr">
@@ -9985,7 +9985,7 @@
       <c r="H137" s="27" t="inlineStr"/>
       <c r="I137" s="13" t="inlineStr">
         <is>
-          <t>No Bank standard found in the asset register - confirm none exists</t>
+          <t>No approved standard found in the asset register. The asset register currently covers AI platform assets only, so a standard owned by another function may exist and not be recorded here - confirm with the owner.</t>
         </is>
       </c>
     </row>
@@ -10120,7 +10120,7 @@
       </c>
       <c r="D141" s="13" t="inlineStr">
         <is>
-          <t>Is there a published Bank standard or method for this?</t>
+          <t>Is there an approved institutional standard, policy or method for this? Set by whoever owns the subject - the platform team, Cybersecurity, Data Management, Legal, HR or EA.</t>
         </is>
       </c>
       <c r="E141" s="25" t="inlineStr">
@@ -10133,7 +10133,7 @@
       <c r="H141" s="27" t="inlineStr"/>
       <c r="I141" s="13" t="inlineStr">
         <is>
-          <t>No Bank standard found in the asset register - confirm none exists</t>
+          <t>No approved standard found in the asset register. The asset register currently covers AI platform assets only, so a standard owned by another function may exist and not be recorded here - confirm with the owner.</t>
         </is>
       </c>
     </row>
@@ -10268,7 +10268,7 @@
       </c>
       <c r="D145" s="13" t="inlineStr">
         <is>
-          <t>Is there a published Bank standard or method for this?</t>
+          <t>Is there an approved institutional standard, policy or method for this? Set by whoever owns the subject - the platform team, Cybersecurity, Data Management, Legal, HR or EA.</t>
         </is>
       </c>
       <c r="E145" s="25" t="inlineStr">
@@ -10281,7 +10281,7 @@
       <c r="H145" s="27" t="inlineStr"/>
       <c r="I145" s="13" t="inlineStr">
         <is>
-          <t>No Bank standard found in the asset register - confirm none exists</t>
+          <t>No approved standard found in the asset register. The asset register currently covers AI platform assets only, so a standard owned by another function may exist and not be recorded here - confirm with the owner.</t>
         </is>
       </c>
     </row>
@@ -10416,7 +10416,7 @@
       </c>
       <c r="D149" s="13" t="inlineStr">
         <is>
-          <t>Is there a published Bank standard or method for this?</t>
+          <t>Is there an approved institutional standard, policy or method for this? Set by whoever owns the subject - the platform team, Cybersecurity, Data Management, Legal, HR or EA.</t>
         </is>
       </c>
       <c r="E149" s="25" t="inlineStr">
@@ -10429,7 +10429,7 @@
       <c r="H149" s="27" t="inlineStr"/>
       <c r="I149" s="13" t="inlineStr">
         <is>
-          <t>No Bank standard found in the asset register - confirm none exists</t>
+          <t>No approved standard found in the asset register. The asset register currently covers AI platform assets only, so a standard owned by another function may exist and not be recorded here - confirm with the owner.</t>
         </is>
       </c>
     </row>
@@ -10564,7 +10564,7 @@
       </c>
       <c r="D153" s="13" t="inlineStr">
         <is>
-          <t>Is there a published Bank standard or method for this?</t>
+          <t>Is there an approved institutional standard, policy or method for this? Set by whoever owns the subject - the platform team, Cybersecurity, Data Management, Legal, HR or EA.</t>
         </is>
       </c>
       <c r="E153" s="25" t="inlineStr">
@@ -10577,7 +10577,7 @@
       <c r="H153" s="27" t="inlineStr"/>
       <c r="I153" s="13" t="inlineStr">
         <is>
-          <t>No Bank standard found in the asset register - confirm none exists</t>
+          <t>No approved standard found in the asset register. The asset register currently covers AI platform assets only, so a standard owned by another function may exist and not be recorded here - confirm with the owner.</t>
         </is>
       </c>
     </row>
@@ -10712,7 +10712,7 @@
       </c>
       <c r="D157" s="13" t="inlineStr">
         <is>
-          <t>Is there a published Bank standard or method for this?</t>
+          <t>Is there an approved institutional standard, policy or method for this? Set by whoever owns the subject - the platform team, Cybersecurity, Data Management, Legal, HR or EA.</t>
         </is>
       </c>
       <c r="E157" s="25" t="inlineStr">
@@ -10725,7 +10725,7 @@
       <c r="H157" s="27" t="inlineStr"/>
       <c r="I157" s="13" t="inlineStr">
         <is>
-          <t>No Bank standard found in the asset register - confirm none exists</t>
+          <t>No approved standard found in the asset register. The asset register currently covers AI platform assets only, so a standard owned by another function may exist and not be recorded here - confirm with the owner.</t>
         </is>
       </c>
     </row>
@@ -10860,7 +10860,7 @@
       </c>
       <c r="D161" s="13" t="inlineStr">
         <is>
-          <t>Is there a published Bank standard or method for this?</t>
+          <t>Is there an approved institutional standard, policy or method for this? Set by whoever owns the subject - the platform team, Cybersecurity, Data Management, Legal, HR or EA.</t>
         </is>
       </c>
       <c r="E161" s="25" t="inlineStr">
@@ -10873,7 +10873,7 @@
       <c r="H161" s="27" t="inlineStr"/>
       <c r="I161" s="13" t="inlineStr">
         <is>
-          <t>No Bank standard found in the asset register - confirm none exists</t>
+          <t>No approved standard found in the asset register. The asset register currently covers AI platform assets only, so a standard owned by another function may exist and not be recorded here - confirm with the owner.</t>
         </is>
       </c>
     </row>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="D165" s="13" t="inlineStr">
         <is>
-          <t>Is there a published Bank standard or method for this?</t>
+          <t>Is there an approved institutional standard, policy or method for this? Set by whoever owns the subject - the platform team, Cybersecurity, Data Management, Legal, HR or EA.</t>
         </is>
       </c>
       <c r="E165" s="25" t="inlineStr">
@@ -11021,7 +11021,7 @@
       <c r="H165" s="27" t="inlineStr"/>
       <c r="I165" s="13" t="inlineStr">
         <is>
-          <t>No Bank standard found in the asset register - confirm none exists</t>
+          <t>No approved standard found in the asset register. The asset register currently covers AI platform assets only, so a standard owned by another function may exist and not be recorded here - confirm with the owner.</t>
         </is>
       </c>
     </row>
@@ -11156,7 +11156,7 @@
       </c>
       <c r="D169" s="13" t="inlineStr">
         <is>
-          <t>Is there a published Bank standard or method for this?</t>
+          <t>Is there an approved institutional standard, policy or method for this? Set by whoever owns the subject - the platform team, Cybersecurity, Data Management, Legal, HR or EA.</t>
         </is>
       </c>
       <c r="E169" s="25" t="inlineStr">
@@ -11169,7 +11169,7 @@
       <c r="H169" s="27" t="inlineStr"/>
       <c r="I169" s="13" t="inlineStr">
         <is>
-          <t>No Bank standard found in the asset register - confirm none exists</t>
+          <t>No approved standard found in the asset register. The asset register currently covers AI platform assets only, so a standard owned by another function may exist and not be recorded here - confirm with the owner.</t>
         </is>
       </c>
     </row>
@@ -11304,7 +11304,7 @@
       </c>
       <c r="D173" s="13" t="inlineStr">
         <is>
-          <t>Is there a published Bank standard or method for this?</t>
+          <t>Is there an approved institutional standard, policy or method for this? Set by whoever owns the subject - the platform team, Cybersecurity, Data Management, Legal, HR or EA.</t>
         </is>
       </c>
       <c r="E173" s="25" t="inlineStr">
@@ -11317,7 +11317,7 @@
       <c r="H173" s="27" t="inlineStr"/>
       <c r="I173" s="13" t="inlineStr">
         <is>
-          <t>No Bank standard found in the asset register - confirm none exists</t>
+          <t>No approved standard found in the asset register. The asset register currently covers AI platform assets only, so a standard owned by another function may exist and not be recorded here - confirm with the owner.</t>
         </is>
       </c>
     </row>
@@ -11452,7 +11452,7 @@
       </c>
       <c r="D177" s="13" t="inlineStr">
         <is>
-          <t>Is there a published Bank standard or method for this?</t>
+          <t>Is there an approved institutional standard, policy or method for this? Set by whoever owns the subject - the platform team, Cybersecurity, Data Management, Legal, HR or EA.</t>
         </is>
       </c>
       <c r="E177" s="25" t="inlineStr">
@@ -11465,7 +11465,7 @@
       <c r="H177" s="27" t="inlineStr"/>
       <c r="I177" s="13" t="inlineStr">
         <is>
-          <t>No Bank standard found in the asset register - confirm none exists</t>
+          <t>No approved standard found in the asset register. The asset register currently covers AI platform assets only, so a standard owned by another function may exist and not be recorded here - confirm with the owner.</t>
         </is>
       </c>
     </row>
@@ -11600,7 +11600,7 @@
       </c>
       <c r="D181" s="13" t="inlineStr">
         <is>
-          <t>Is there a published Bank standard or method for this?</t>
+          <t>Is there an approved institutional standard, policy or method for this? Set by whoever owns the subject - the platform team, Cybersecurity, Data Management, Legal, HR or EA.</t>
         </is>
       </c>
       <c r="E181" s="25" t="inlineStr">
@@ -11613,7 +11613,7 @@
       <c r="H181" s="27" t="inlineStr"/>
       <c r="I181" s="13" t="inlineStr">
         <is>
-          <t>No Bank standard found in the asset register - confirm none exists</t>
+          <t>No approved standard found in the asset register. The asset register currently covers AI platform assets only, so a standard owned by another function may exist and not be recorded here - confirm with the owner.</t>
         </is>
       </c>
     </row>
@@ -11748,7 +11748,7 @@
       </c>
       <c r="D185" s="13" t="inlineStr">
         <is>
-          <t>Is there a published Bank standard or method for this?</t>
+          <t>Is there an approved institutional standard, policy or method for this? Set by whoever owns the subject - the platform team, Cybersecurity, Data Management, Legal, HR or EA.</t>
         </is>
       </c>
       <c r="E185" s="25" t="inlineStr">
@@ -11761,7 +11761,7 @@
       <c r="H185" s="27" t="inlineStr"/>
       <c r="I185" s="13" t="inlineStr">
         <is>
-          <t>No Bank standard found in the asset register - confirm none exists</t>
+          <t>No approved standard found in the asset register. The asset register currently covers AI platform assets only, so a standard owned by another function may exist and not be recorded here - confirm with the owner.</t>
         </is>
       </c>
     </row>
@@ -11896,7 +11896,7 @@
       </c>
       <c r="D189" s="13" t="inlineStr">
         <is>
-          <t>Is there a published Bank standard or method for this?</t>
+          <t>Is there an approved institutional standard, policy or method for this? Set by whoever owns the subject - the platform team, Cybersecurity, Data Management, Legal, HR or EA.</t>
         </is>
       </c>
       <c r="E189" s="25" t="inlineStr">
@@ -11909,7 +11909,7 @@
       <c r="H189" s="27" t="inlineStr"/>
       <c r="I189" s="13" t="inlineStr">
         <is>
-          <t>No Bank standard found in the asset register - confirm none exists</t>
+          <t>No approved standard found in the asset register. The asset register currently covers AI platform assets only, so a standard owned by another function may exist and not be recorded here - confirm with the owner.</t>
         </is>
       </c>
     </row>
@@ -12044,7 +12044,7 @@
       </c>
       <c r="D193" s="13" t="inlineStr">
         <is>
-          <t>Is there a published Bank standard or method for this?</t>
+          <t>Is there an approved institutional standard, policy or method for this? Set by whoever owns the subject - the platform team, Cybersecurity, Data Management, Legal, HR or EA.</t>
         </is>
       </c>
       <c r="E193" s="25" t="inlineStr">
@@ -12057,7 +12057,7 @@
       <c r="H193" s="27" t="inlineStr"/>
       <c r="I193" s="13" t="inlineStr">
         <is>
-          <t>No Bank standard found in the asset register - confirm none exists</t>
+          <t>No approved standard found in the asset register. The asset register currently covers AI platform assets only, so a standard owned by another function may exist and not be recorded here - confirm with the owner.</t>
         </is>
       </c>
     </row>
@@ -12192,7 +12192,7 @@
       </c>
       <c r="D197" s="13" t="inlineStr">
         <is>
-          <t>Is there a published Bank standard or method for this?</t>
+          <t>Is there an approved institutional standard, policy or method for this? Set by whoever owns the subject - the platform team, Cybersecurity, Data Management, Legal, HR or EA.</t>
         </is>
       </c>
       <c r="E197" s="25" t="inlineStr">
@@ -12205,7 +12205,7 @@
       <c r="H197" s="27" t="inlineStr"/>
       <c r="I197" s="13" t="inlineStr">
         <is>
-          <t>No Bank standard found in the asset register - confirm none exists</t>
+          <t>No approved standard found in the asset register. The asset register currently covers AI platform assets only, so a standard owned by another function may exist and not be recorded here - confirm with the owner.</t>
         </is>
       </c>
     </row>
@@ -12340,7 +12340,7 @@
       </c>
       <c r="D201" s="13" t="inlineStr">
         <is>
-          <t>Is there a published Bank standard or method for this?</t>
+          <t>Is there an approved institutional standard, policy or method for this? Set by whoever owns the subject - the platform team, Cybersecurity, Data Management, Legal, HR or EA.</t>
         </is>
       </c>
       <c r="E201" s="25" t="inlineStr">
@@ -12353,7 +12353,7 @@
       <c r="H201" s="27" t="inlineStr"/>
       <c r="I201" s="13" t="inlineStr">
         <is>
-          <t>No Bank standard found in the asset register - confirm none exists</t>
+          <t>No approved standard found in the asset register. The asset register currently covers AI platform assets only, so a standard owned by another function may exist and not be recorded here - confirm with the owner.</t>
         </is>
       </c>
     </row>
@@ -12488,7 +12488,7 @@
       </c>
       <c r="D205" s="13" t="inlineStr">
         <is>
-          <t>Is there a published Bank standard or method for this?</t>
+          <t>Is there an approved institutional standard, policy or method for this? Set by whoever owns the subject - the platform team, Cybersecurity, Data Management, Legal, HR or EA.</t>
         </is>
       </c>
       <c r="E205" s="25" t="inlineStr">
@@ -12501,7 +12501,7 @@
       <c r="H205" s="27" t="inlineStr"/>
       <c r="I205" s="13" t="inlineStr">
         <is>
-          <t>No Bank standard found in the asset register - confirm none exists</t>
+          <t>No approved standard found in the asset register. The asset register currently covers AI platform assets only, so a standard owned by another function may exist and not be recorded here - confirm with the owner.</t>
         </is>
       </c>
     </row>
@@ -12636,7 +12636,7 @@
       </c>
       <c r="D209" s="13" t="inlineStr">
         <is>
-          <t>Is there a published Bank standard or method for this?</t>
+          <t>Is there an approved institutional standard, policy or method for this? Set by whoever owns the subject - the platform team, Cybersecurity, Data Management, Legal, HR or EA.</t>
         </is>
       </c>
       <c r="E209" s="25" t="inlineStr">
@@ -12649,7 +12649,7 @@
       <c r="H209" s="27" t="inlineStr"/>
       <c r="I209" s="13" t="inlineStr">
         <is>
-          <t>No Bank standard found in the asset register - confirm none exists</t>
+          <t>No approved standard found in the asset register. The asset register currently covers AI platform assets only, so a standard owned by another function may exist and not be recorded here - confirm with the owner.</t>
         </is>
       </c>
     </row>

--- a/out/AI-Capability-Model.xlsx
+++ b/out/AI-Capability-Model.xlsx
@@ -4669,7 +4669,7 @@
     <row r="55" ht="46" customHeight="1">
       <c r="A55" s="22" t="inlineStr">
         <is>
-          <t>READ ONLY - every column is computed. Observations are edited on sheet 2. Scale: Capability level. Adapted from ISO/IEC 33020:2019 (process measurement framework). Simplified: four observations rather than five process attributes, three values rather than the standard's four-point N-P-L-F scale.  Levels 4 and 5 are defined but not derivable: this model does not yet collect threshold monitoring or improvement-cycle observations. 3 is the highest level currently reachable.</t>
+          <t>READ ONLY - every column is computed. Observations are edited on sheet 2. Scale: Capability level. Adapted from ISO/IEC 33020:2019 (process measurement framework). Simplified: four observations rather than five process attributes, three values rather than the standard's four-point N-P-L-F scale.  Level 3 is the highest this model can currently derive. Levels 4 and 5 are defined but need observations nobody collects yet - threshold monitoring and a closed improvement cycle - so a capability at 3 is at the top of what is measured here, not at the top of the scale. Level 3 also reads conformance from a standard and a practice co-existing; it is not separately evidenced.</t>
         </is>
       </c>
     </row>
